--- a/dist/sample/ccocr_v260317.xlsx
+++ b/dist/sample/ccocr_v260317.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cy\dyna\ccocr_HEAD\CURRENT_TASK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cy/Desktop/CLAUDEs/ccocr/dist/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AA01BA-1CF0-4D3F-B2E6-DC63D6F5FA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC015DD-BF95-4040-AD14-2224B228466E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9EFF4B2A-F56A-407A-B23E-F71D54028BE8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15840" xr2:uid="{9EFF4B2A-F56A-407A-B23E-F71D54028BE8}"/>
   </bookViews>
   <sheets>
     <sheet name="global" sheetId="22" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="184">
   <si>
     <t>↓黄色部分をマウスで選んでください</t>
     <rPh sb="1" eb="3">
@@ -993,6 +993,9 @@
   </si>
   <si>
     <t>BOTH</t>
+  </si>
+  <si>
+    <t>マクロ付きエクセル</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1405,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1418,7 +1421,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1715,12 +1718,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB28F614-B26B-45A7-8DE0-A8C7655D4033}">
   <dimension ref="B2:D41"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.625" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
-    <col min="3" max="3" width="3.625" customWidth="1"/>
-    <col min="4" max="4" width="67.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="67.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -1800,7 +1803,7 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="34" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D22" t="s">
         <v>181</v>
@@ -1878,7 +1881,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="8"/>
-  <dataValidations count="8">
+  <dataValidations disablePrompts="1" count="8">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B27:B28" xr:uid="{CCD77B2C-FFB0-46DC-B824-E8469474379B}">
       <formula1>"NOT 2UP,２ＵＰ"</formula1>
     </dataValidation>
@@ -1901,7 +1904,7 @@
       <formula1>"PNG変換する,PNG変換しない,両方"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22" xr:uid="{A41345A1-BD4E-4647-AEBC-AB0B150E3602}">
-      <formula1>"マクロ付きエクセル,WEB,両方,確認画面不要"</formula1>
+      <formula1>"マクロ付きエクセル,WEB,確認画面不要"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1912,9 +1915,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FA4BEB-BEDC-874D-A3C0-CC1658D44972}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
@@ -1930,7 +1933,7 @@
       </c>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:5" ht="95.1" customHeight="1">
+    <row r="2" spans="1:5" ht="95" customHeight="1">
       <c r="A2" s="32" t="s">
         <v>67</v>
       </c>
@@ -1961,7 +1964,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="15">
       <c r="A5" s="4" t="s">
         <v>78</v>
       </c>
@@ -2010,10 +2013,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E46523C-3053-4F7E-88E3-D4CC7FD2F242}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2030,7 +2033,7 @@
       </c>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:5" ht="95.1" customHeight="1">
+    <row r="2" spans="1:5" ht="95" customHeight="1">
       <c r="A2" s="32" t="s">
         <v>67</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="15">
       <c r="A5" s="4" t="s">
         <v>107</v>
       </c>
@@ -2110,7 +2113,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5BC1C2-71E7-5948-B348-591A51C58EB3}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
   </cols>
@@ -2178,7 +2181,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2549886-AD12-4D04-8109-A9ECFC7355C4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -2194,24 +2197,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8CA3F8-1815-46B0-933E-256974E16251}">
   <dimension ref="A1:P177"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="11.625" customWidth="1"/>
-    <col min="9" max="9" width="10.875" customWidth="1"/>
-    <col min="10" max="10" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="27.875" customWidth="1"/>
-    <col min="12" max="12" width="8.625" customWidth="1"/>
-    <col min="13" max="13" width="6.625" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="27.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" customWidth="1"/>
+    <col min="14" max="14" width="7.1640625" customWidth="1"/>
     <col min="15" max="15" width="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="100.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="100.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="39" customHeight="1">
@@ -2252,7 +2255,7 @@
       </c>
       <c r="P1" s="16"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="15">
       <c r="A2" s="25" t="s">
         <v>23</v>
       </c>
@@ -2298,7 +2301,7 @@
       <c r="O2" s="43"/>
       <c r="P2" s="16"/>
     </row>
-    <row r="3" spans="1:16" ht="175.5" hidden="1">
+    <row r="3" spans="1:16" ht="195" hidden="1">
       <c r="A3" s="20" t="s">
         <v>31</v>
       </c>
@@ -5359,23 +5362,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF8AAC49-95F2-4574-BADF-81F5C0E8FC6C}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24.375" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="3" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="16.125" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="11.625" customWidth="1"/>
-    <col min="9" max="9" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="38.125" customWidth="1"/>
-    <col min="12" max="12" width="5.875" customWidth="1"/>
-    <col min="13" max="13" width="5.625" customWidth="1"/>
-    <col min="14" max="14" width="8.375" customWidth="1"/>
-    <col min="15" max="15" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="38.1640625" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.1640625" customWidth="1"/>
     <col min="16" max="16" width="7.5" customWidth="1"/>
     <col min="17" max="17" width="3" bestFit="1" customWidth="1"/>
   </cols>
@@ -5468,7 +5471,7 @@
       </c>
       <c r="Q2" s="49"/>
     </row>
-    <row r="3" spans="1:17" ht="164.1" hidden="1" customHeight="1">
+    <row r="3" spans="1:17" ht="164" hidden="1" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>55</v>
       </c>
@@ -5584,7 +5587,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" ht="15">
       <c r="A7" s="4" t="s">
         <v>150</v>
       </c>
@@ -5607,7 +5610,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="40"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" ht="15">
       <c r="A8" s="4" t="s">
         <v>142</v>
       </c>
@@ -5630,7 +5633,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" ht="15">
       <c r="A9" s="4" t="s">
         <v>132</v>
       </c>
@@ -5653,7 +5656,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" ht="15">
       <c r="A10" s="4" t="s">
         <v>128</v>
       </c>
@@ -5676,7 +5679,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" ht="15">
       <c r="A11" s="4" t="s">
         <v>127</v>
       </c>
@@ -5743,7 +5746,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" ht="15">
       <c r="A14" s="4" t="s">
         <v>155</v>
       </c>
@@ -5768,7 +5771,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" ht="15">
       <c r="A15" s="4" t="s">
         <v>157</v>
       </c>
@@ -5793,7 +5796,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" ht="15">
       <c r="A16" s="4" t="s">
         <v>159</v>
       </c>
@@ -5921,7 +5924,7 @@
       </c>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" ht="15">
       <c r="A20" s="4" t="s">
         <v>165</v>
       </c>
@@ -5960,7 +5963,7 @@
       </c>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" ht="15">
       <c r="A21" s="4" t="s">
         <v>167</v>
       </c>
@@ -5999,7 +6002,7 @@
       </c>
       <c r="Q21" s="5"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" ht="15">
       <c r="A22" s="4" t="s">
         <v>169</v>
       </c>
@@ -6412,23 +6415,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FDB77A3-BE7D-FF43-AB03-A4324CB92ED7}">
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24.375" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="3" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="16.125" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="11.625" customWidth="1"/>
-    <col min="9" max="9" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="38.125" customWidth="1"/>
-    <col min="12" max="12" width="5.875" customWidth="1"/>
-    <col min="13" max="13" width="5.625" customWidth="1"/>
-    <col min="14" max="14" width="8.375" customWidth="1"/>
-    <col min="15" max="15" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="38.1640625" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.1640625" customWidth="1"/>
     <col min="16" max="16" width="7.5" customWidth="1"/>
     <col min="17" max="17" width="3" bestFit="1" customWidth="1"/>
   </cols>
@@ -6521,7 +6524,7 @@
       </c>
       <c r="Q2" s="49"/>
     </row>
-    <row r="3" spans="1:17" ht="164.1" hidden="1" customHeight="1">
+    <row r="3" spans="1:17" ht="164" hidden="1" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>55</v>
       </c>
@@ -7262,22 +7265,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79998458-85D8-A14F-BBAE-93ACC93828CB}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24.375" customWidth="1"/>
-    <col min="3" max="3" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="16.125" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="11.625" customWidth="1"/>
-    <col min="9" max="9" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="9.625" customWidth="1"/>
-    <col min="12" max="12" width="22.375" customWidth="1"/>
-    <col min="13" max="14" width="19.125" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="13" max="14" width="19.1640625" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="25.125" customWidth="1"/>
+    <col min="16" max="16" width="25.1640625" customWidth="1"/>
     <col min="17" max="17" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7369,7 +7372,7 @@
       </c>
       <c r="Q2" s="49"/>
     </row>
-    <row r="3" spans="1:17" ht="164.1" customHeight="1">
+    <row r="3" spans="1:17" ht="164" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>55</v>
       </c>
@@ -7652,12 +7655,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C43093-91FF-704E-9FBA-8CEB5A1CF880}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
-    <col min="4" max="5" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7676,7 +7679,7 @@
       </c>
       <c r="G1" s="16"/>
     </row>
-    <row r="2" spans="1:9" ht="27">
+    <row r="2" spans="1:9" ht="30">
       <c r="A2" s="32" t="s">
         <v>67</v>
       </c>
@@ -7957,9 +7960,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E2832D-079F-E048-8596-6C1112C2D44C}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="45" customHeight="1">
@@ -7975,7 +7978,7 @@
       </c>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:5" ht="95.1" customHeight="1">
+    <row r="2" spans="1:5" ht="95" customHeight="1">
       <c r="A2" s="32" t="s">
         <v>67</v>
       </c>
@@ -8006,7 +8009,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="15">
       <c r="A5" s="4" t="s">
         <v>78</v>
       </c>
@@ -8024,7 +8027,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="4" t="s">
         <v>81</v>
       </c>
@@ -8061,10 +8064,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8625CCA2-2961-1449-A9DB-E74F91214DB4}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="54" customHeight="1">
@@ -8113,7 +8116,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="4" t="s">
         <v>78</v>
       </c>
@@ -8137,7 +8140,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="4" t="s">
         <v>81</v>
       </c>
